--- a/stories/arbres/ATOM-SEC.MAI.002-06.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Didier aide papa dans la cuisine. Papa coupe le pain. Didier pose les serviettes. Sur la table, il y a un petit pot. Didier ne le connaît pas. C'est inconnu. Ses mains restent près de lui. Didier va vers papa. Papa, c'est l'adulte. Didier dit : je ne connais pas. Je demande. Papa prend le pot. Papa dit : merci d'avoir demandé. L'inconnu, on le montre à un adulte. Didier pose les mains sur les serviettes. Plus tard, dans le jardin, Didier voit une baie brillante. Il ne la connaît pas. C'est inconnu. Il va vers papa. Il demande. Papa le rejoint. Papa dit : on demande avant. Didier a les pieds au sol, près de l'adulte.</t>
+          <t>Didier aide papa dans la cuisine. Papa coupe le pain. Didier pose les serviettes. Sur la table, il y a un petit pot. Didier ne le connaît pas. C'est inconnu. Ses mains restent près de lui. Didier va vers papa. Papa, c'est l'adulte. Je ne connais pas. Je demande. Papa prend le pot. Merci d'avoir demandé. L'inconnu, on le montre à un adulte. Didier pose les mains sur les serviettes. Plus tard, dans le jardin, Didier voit une baie brillante. Il ne la connaît pas. C'est inconnu. Il va vers papa. Il demande. Papa le rejoint. On demande avant. Didier a les pieds au sol, près de l'adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Didier aide papa dans la cuisine. Papa coupe le pain. Didier pose les serviettes. Sur la table, il y a un petit pot. Didier ne le connaît pas. C'est inconnu. Ses mains restent près de lui. Didier va vers papa. Papa, c'est l'adulte.
+enfant-m|Je ne connais pas. Je demande. Papa prend le pot.
+papa|Merci d'avoir demandé. L'inconnu, on le montre à un adulte.
+narrateur|Didier pose les mains sur les serviettes. Plus tard, dans le jardin, Didier voit une baie brillante. Il ne la connaît pas. C'est inconnu. Il va vers papa. Il demande. Papa le rejoint.
+papa|On demande avant.
+narrateur|Didier a les pieds au sol, près de l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1473,6 +1499,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Didier voit quelque chose d'inconnu. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1645,6 +1676,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Didier a demandé. L'inconnu, on le montre à un adulte. Papa a écouté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1843,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Didier pose une serviette à sa place. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2010,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2050,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-06.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 narrateur|Didier a les pieds au sol, près de l'adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1506,6 +1512,7 @@
           <t>narrateur|Didier voit quelque chose d'inconnu. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1681,6 +1688,7 @@
           <t>narrateur|Didier a demandé. L'inconnu, on le montre à un adulte. Papa a écouté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1848,6 +1856,7 @@
           <t>narrateur|Didier pose une serviette à sa place. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2015,6 +2024,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2033,7 +2043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2057,6 +2067,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2258,6 +2282,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.MAI.002-06.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Didier demande avant l'inconnu</t>
+          <t>Le petit pot de Nino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La vitre est embuée. Nino pose les serviettes. Un petit pot inconnu attend. Il demande à papa. Au jardin, une baie brille. Il demande encore.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Didier aide papa dans la cuisine. Papa coupe le pain. Didier pose les serviettes. Sur la table, il y a un petit pot. Didier ne le connaît pas. C'est inconnu. Ses mains restent près de lui. Didier va vers papa. Papa, c'est l'adulte. Je ne connais pas. Je demande. Papa prend le pot. Merci d'avoir demandé. L'inconnu, on le montre à un adulte. Didier pose les mains sur les serviettes. Plus tard, dans le jardin, Didier voit une baie brillante. Il ne la connaît pas. C'est inconnu. Il va vers papa. Il demande. Papa le rejoint. On demande avant. Didier a les pieds au sol, près de l'adulte.</t>
+          <t>La vitre de la cuisine est toute embuée. Une goutte glisse, toute lente. Ça sent la soupe, bien chaude. Le bois de la table est lisse. Il y a des miettes de pain. Une serviette jaune attend, pliée. Un rayon traverse la buée. Il fait un rond sur le bois. Maman remue la soupe. La cuillère fait un petit bruit. Tu as senti la soupe, Nino ? Oui, maman. C'est chaud. Le pain est prêt. Tu poses les serviettes ? En ce moment, Nino prend la serviette jaune. Le tissu est un peu rêche. Il la pose près de l'assiette. Bravo, Nino. Elle est bien à sa place. Sur la table, il y a un petit pot. Nino ne le connaît pas. C'est inconnu. Ses mains restent près de lui. Il va vers papa. Papa, c'est l'adulte. Papa, je ne connais pas. Je demande. Merci d'avoir demandé. L'inconnu, on le montre à un adulte. Papa prend le petit pot. Il le pose plus loin. Tu as bien demandé, Nino. C'est du bon travail. J'ai demandé. Oui. On peut demander. Demander à l'adulte. Demander. Nino pose encore une serviette. Ses mains restent près de lui. Tu as fini les serviettes ? Oui, papa. Bravo. Plus tard, la porte du jardin s'ouvre. L'air sent l'herbe coupée. Une petite baie brille au soleil. Elle est rouge, toute ronde. Nino ne la connaît pas. C'est inconnu. Ses mains restent près de lui. Il va vers papa. Papa, je ne connais pas. Je demande. Je viens. On demande avant. Papa rejoint Nino. Nino reste près de l'adulte. Tu as encore demandé. Bravo. L'inconnu, on le montre. Oui. À un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1324,76 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Didier aide papa dans la cuisine. Papa coupe le pain. Didier pose les serviettes. Sur la table, il y a un petit pot. Didier ne le connaît pas. C'est inconnu. Ses mains restent près de lui. Didier va vers papa. Papa, c'est l'adulte.
-enfant-m|Je ne connais pas. Je demande. Papa prend le pot.
-papa|Merci d'avoir demandé. L'inconnu, on le montre à un adulte.
-narrateur|Didier pose les mains sur les serviettes. Plus tard, dans le jardin, Didier voit une baie brillante. Il ne la connaît pas. C'est inconnu. Il va vers papa. Il demande. Papa le rejoint.
+          <t>narrateur|La vitre de la cuisine est toute embuée.
+narrateur|Une goutte glisse, toute lente.
+narrateur|Ça sent la soupe, bien chaude.
+narrateur|Le bois de la table est lisse.
+narrateur|Il y a des miettes de pain.
+narrateur|Une serviette jaune attend, pliée.
+narrateur|Un rayon traverse la buée.
+narrateur|Il fait un rond sur le bois.
+narrateur|Maman remue la soupe.
+narrateur|La cuillère fait un petit bruit.
+maman|Tu as senti la soupe, Nino ?
+enfant-m|Oui, maman.
+enfant-m|C'est chaud.
+papa|Le pain est prêt.
+papa|Tu poses les serviettes ?
+narrateur|En ce moment, Nino prend la serviette jaune.
+narrateur|Le tissu est un peu rêche.
+narrateur|Il la pose près de l'assiette.
+maman|Bravo, Nino.
+maman|Elle est bien à sa place.
+narrateur|Sur la table, il y a un petit pot.
+narrateur|Nino ne le connaît pas.
+narrateur|C'est inconnu.
+narrateur|Ses mains restent près de lui.
+narrateur|Il va vers papa.
+narrateur|Papa, c'est l'adulte.
+enfant-m|Papa, je ne connais pas.
+enfant-m|Je demande.
+papa|Merci d'avoir demandé.
+papa|L'inconnu, on le montre à un adulte.
+narrateur|Papa prend le petit pot.
+narrateur|Il le pose plus loin.
+maman|Tu as bien demandé, Nino.
+maman|C'est du bon travail.
+enfant-m|J'ai demandé.
+papa|Oui.
+papa|On peut demander.
+papa|Demander à l'adulte.
+enfant-m|Demander.
+narrateur|Nino pose encore une serviette.
+narrateur|Ses mains restent près de lui.
+papa|Tu as fini les serviettes ?
+enfant-m|Oui, papa.
+papa|Bravo.
+narrateur|Plus tard, la porte du jardin s'ouvre.
+narrateur|L'air sent l'herbe coupée.
+narrateur|Une petite baie brille au soleil.
+narrateur|Elle est rouge, toute ronde.
+narrateur|Nino ne la connaît pas.
+narrateur|C'est inconnu.
+narrateur|Ses mains restent près de lui.
+narrateur|Il va vers papa.
+enfant-m|Papa, je ne connais pas.
+enfant-m|Je demande.
+papa|Je viens.
 papa|On demande avant.
-narrateur|Didier a les pieds au sol, près de l'adulte.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Papa rejoint Nino.
+narrateur|Nino reste près de l'adulte.
+maman|Tu as encore demandé.
+maman|Bravo.
+enfant-m|L'inconnu, on le montre.
+papa|Oui.
+papa|À un adulte.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>soupe,porte</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,7 +1418,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Didier voit quelque chose d'inconnu. Que fait-il ?</t>
+          <t>Nino voit quelque chose d'inconnu. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1509,7 +1582,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Didier voit quelque chose d'inconnu. Que fait-il ?</t>
+          <t>narrateur|Nino voit quelque chose d'inconnu.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1537,7 +1611,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Didier a demandé. L'inconnu, on le montre à un adulte. Papa a écouté.</t>
+          <t>Nino a demandé. L'inconnu, on le montre à un adulte. Merci d'avoir demandé. Papa a écouté. Bravo, Nino. J'ai demandé à l'adulte. Oui. C'est du bon travail. Tu as fini de montrer l'inconnu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,7 +1759,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Didier a demandé. L'inconnu, on le montre à un adulte. Papa a écouté.</t>
+          <t>narrateur|Nino a demandé.
+narrateur|L'inconnu, on le montre à un adulte.
+papa|Merci d'avoir demandé.
+maman|Papa a écouté.
+papa|Bravo, Nino.
+enfant-m|J'ai demandé à l'adulte.
+maman|Oui.
+maman|C'est du bon travail.
+papa|Tu as fini de montrer l'inconnu ?
+enfant-m|Oui, papa.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1713,7 +1796,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Didier pose une serviette à sa place. Papa sourit.</t>
+          <t>Nino pose une dernière serviette. Elle est jaune, bien à sa place. La soupe est prête. Tu viens t'asseoir ? Oui, maman. Les mains restent près de toi. On demande, d'accord ? D'accord. La vitre n'est plus embuée. Un oiseau chante dans le jardin. La soupe fume encore un peu. Tu as fait du bon travail. Bravo, Nino. On a demandé, tous les deux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1853,7 +1936,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Didier pose une serviette à sa place. Papa sourit.</t>
+          <t>narrateur|Nino pose une dernière serviette.
+narrateur|Elle est jaune, bien à sa place.
+maman|La soupe est prête.
+maman|Tu viens t'asseoir ?
+enfant-m|Oui, maman.
+papa|Les mains restent près de toi.
+papa|On demande, d'accord ?
+enfant-m|D'accord.
+narrateur|La vitre n'est plus embuée.
+narrateur|Un oiseau chante dans le jardin.
+narrateur|La soupe fume encore un peu.
+maman|Tu as fait du bon travail.
+papa|Bravo, Nino.
+papa|On a demandé, tous les deux.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1881,7 +1977,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai demandé. Papa a pris le petit pot. Bravo. Tu as fait du bon travail. La serviette jaune reste à sa place. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2021,7 +2117,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai demandé.
+enfant-m|Papa a pris le petit pot.
+papa|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|La serviette jaune reste à sa place.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2043,7 +2144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2081,6 +2182,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-06.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vitre de la cuisine est toute embuée. Une goutte glisse, toute lente. Ça sent la soupe, bien chaude. Le bois de la table est lisse. Il y a des miettes de pain. Une serviette jaune attend, pliée. Un rayon traverse la buée. Il fait un rond sur le bois. Maman remue la soupe. La cuillère fait un petit bruit. Tu as senti la soupe, Nino ? Oui, maman. C'est chaud. Le pain est prêt. Tu poses les serviettes ? En ce moment, Nino prend la serviette jaune. Le tissu est un peu rêche. Il la pose près de l'assiette. Bravo, Nino. Elle est bien à sa place. Sur la table, il y a un petit pot. Nino ne le connaît pas. C'est inconnu. Ses mains restent près de lui. Il va vers papa. Papa, c'est l'adulte. Papa, je ne connais pas. Je demande. Merci d'avoir demandé. L'inconnu, on le montre à un adulte. Papa prend le petit pot. Il le pose plus loin. Tu as bien demandé, Nino. C'est du bon travail. J'ai demandé. Oui. On peut demander. Demander à l'adulte. Demander. Nino pose encore une serviette. Ses mains restent près de lui. Tu as fini les serviettes ? Oui, papa. Bravo. Plus tard, la porte du jardin s'ouvre. L'air sent l'herbe coupée. Une petite baie brille au soleil. Elle est rouge, toute ronde. Nino ne la connaît pas. C'est inconnu. Ses mains restent près de lui. Il va vers papa. Papa, je ne connais pas. Je demande. Je viens. On demande avant. Papa rejoint Nino. Nino reste près de l'adulte. Tu as encore demandé. Bravo. L'inconnu, on le montre. Oui. À un adulte.</t>
+          <t>La vitre de la cuisine est toute embuée. Une goutte glisse, toute lente. Ça sent la soupe, bien chaude. Le bois de la table est lisse. Il y a des miettes de pain. Une serviette jaune attend, pliée. Un rayon traverse la buée. Il fait un rond sur le bois. Maman remue la soupe. La cuillère fait un petit bruit. Tu as senti la soupe, Nino ? Oui, maman. C'est chaud. Le pain est prêt. Tu poses les serviettes ? En ce moment, Nino prend la serviette jaune. Le tissu est un peu rêche. Il la pose près de l'assiette. Bravo, Nino. Elle est bien à sa place. Sur la table, il y a un petit pot. Nino ne le connaît pas. C'est inconnu. Ses mains restent près de lui. Il va vers papa. Papa, c'est l'adulte. Papa, je ne connais pas. Je demande. Merci d'avoir demandé. L'inconnu, on le montre à un adulte. Papa prend le petit pot. Il le pose plus loin. Tu as bien demandé, Nino. J'ai demandé. Oui. On peut demander. Demander à l'adulte. Demander. Nino pose encore une serviette. Ses mains restent près de lui. Tu as fini les serviettes ? Oui, papa. Bravo. Plus tard, la porte du jardin s'ouvre. L'air sent l'herbe coupée. Une petite baie brille au soleil. Elle est rouge, toute ronde. Nino ne la connaît pas. C'est inconnu. Ses mains restent près de lui. Il va vers papa. Papa, je ne connais pas. Je demande. Je viens. On demande avant. Papa rejoint Nino. Nino reste près de l'adulte. Tu as encore demandé. Bravo. L'inconnu, on le montre. Oui. À un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Didier aide papa dans la cuisine. Papa coupe le pain. Didier pose les serviettes. Sur la table, il y a un petit pot. Didier ne le connaît pas. C'est &lt;emphasis level="moderate"&gt;inconnu&lt;/emphasis&gt;. Ses mains restent près de lui. Didier va vers papa. Papa, c'est l'adulte. Didier dit : je ne connais pas. Je demande. Papa prend le pot. Papa dit : merci d'avoir demandé. L'inconnu, on le montre à un adulte. Didier pose les mains sur les serviettes. Plus tard, dans le jardin, Didier voit une baie brillante. Il ne la connaît pas. C'est inconnu. Il va vers papa. Il demande. Papa le rejoint. Papa dit : on demande avant. Didier a les pieds au sol, près de l'adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La vitre de la cuisine est toute embuée. Une goutte glisse, toute lente. Ça sent la soupe, bien chaude. Le bois de la table est lisse. Il y a des miettes de pain. Une serviette jaune attend, pliée. Un rayon traverse la buée. Il fait un rond sur le bois. Maman remue la soupe. La cuillère fait un petit bruit. Tu as senti la soupe, Nino ? Oui, maman. C'est chaud. Le pain est prêt. Tu poses les serviettes ? En ce moment, Nino prend la serviette jaune. Le tissu est un peu rêche. Il la pose près de l'assiette. Bravo, Nino. Elle est bien à sa place. Sur la table, il y a un petit pot. Nino ne le connaît pas. C'est inconnu. Ses mains restent près de lui. Il va vers papa. Papa, c'est l'adulte. Papa, je ne connais pas. Je demande. Merci d'avoir demandé. L'inconnu, on le montre à un adulte. Papa prend le petit pot. Il le pose plus loin. Tu as bien demandé, Nino. J'ai demandé. Oui. On peut demander. Demander à l'adulte. Demander. Nino pose encore une serviette. Ses mains restent près de lui. Tu as fini les serviettes ? Oui, papa. Bravo. Plus tard, la porte du jardin s'ouvre. L'air sent l'herbe coupée. Une petite baie brille au soleil. Elle est rouge, toute ronde. Nino ne la connaît pas. C'est inconnu. Ses mains restent près de lui. Il va vers papa. Papa, je ne connais pas. Je demande. Je viens. On demande avant. Papa rejoint Nino. Nino reste près de l'adulte. Tu as encore demandé. Bravo. L'inconnu, on le montre. Oui. À un adulte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1357,7 +1357,6 @@
 narrateur|Papa prend le petit pot.
 narrateur|Il le pose plus loin.
 maman|Tu as bien demandé, Nino.
-maman|C'est du bon travail.
 enfant-m|J'ai demandé.
 papa|Oui.
 papa|On peut demander.
@@ -1423,7 +1422,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Didier voit quelque chose d'&lt;emphasis level="moderate"&gt;inconnu&lt;/emphasis&gt;. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino voit quelque chose d'inconnu. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1586,7 +1585,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1611,12 +1609,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a demandé. L'inconnu, on le montre à un adulte. Merci d'avoir demandé. Papa a écouté. Bravo, Nino. J'ai demandé à l'adulte. Oui. C'est du bon travail. Tu as fini de montrer l'inconnu ? Oui, papa.</t>
+          <t>Nino a demandé. L'inconnu, on le montre à un adulte. Merci d'avoir demandé. Papa a écouté. Bravo, Nino. J'ai demandé à l'adulte. Oui. Tu as fini de montrer l'inconnu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Didier a demandé. L'&lt;emphasis level="moderate"&gt;inconnu&lt;/emphasis&gt;, on le montre à un adulte. Papa a écouté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a demandé. L'inconnu, on le montre à un adulte. Merci d'avoir demandé. Papa a écouté. Bravo, Nino. J'ai demandé à l'adulte. Oui. Tu as fini de montrer l'inconnu ? Oui, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1766,12 +1764,10 @@
 papa|Bravo, Nino.
 enfant-m|J'ai demandé à l'adulte.
 maman|Oui.
-maman|C'est du bon travail.
 papa|Tu as fini de montrer l'inconnu ?
 enfant-m|Oui, papa.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1796,12 +1792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nino pose une dernière serviette. Elle est jaune, bien à sa place. La soupe est prête. Tu viens t'asseoir ? Oui, maman. Les mains restent près de toi. On demande, d'accord ? D'accord. La vitre n'est plus embuée. Un oiseau chante dans le jardin. La soupe fume encore un peu. Tu as fait du bon travail. Bravo, Nino. On a demandé, tous les deux.</t>
+          <t>Nino pose une dernière serviette. Elle est jaune, bien à sa place. La soupe est prête. Tu viens t'asseoir ? Oui, maman. Les mains restent près de toi. On demande, d'accord ? D'accord. La vitre n'est plus embuée. Un oiseau chante dans le jardin. La soupe fume encore un peu. Bravo, Nino. On a demandé, tous les deux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Didier pose une serviette à sa place. Papa sourit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino pose une dernière serviette. Elle est jaune, bien à sa place. La soupe est prête. Tu viens t'asseoir ? Oui, maman. Les mains restent près de toi. On demande, d'accord ? D'accord. La vitre n'est plus embuée. Un oiseau chante dans le jardin. La soupe fume encore un peu. Bravo, Nino. On a demandé, tous les deux.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1947,12 +1943,10 @@
 narrateur|La vitre n'est plus embuée.
 narrateur|Un oiseau chante dans le jardin.
 narrateur|La soupe fume encore un peu.
-maman|Tu as fait du bon travail.
 papa|Bravo, Nino.
 papa|On a demandé, tous les deux.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1977,12 +1971,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai demandé. Papa a pris le petit pot. Bravo. Tu as fait du bon travail. La serviette jaune reste à sa place. L'histoire est finie.</t>
+          <t>J'ai demandé. Papa a pris le petit pot. Bravo. La serviette jaune reste à sa place.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai demandé. Papa a pris le petit pot. Bravo. La serviette jaune reste à sa place.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2120,12 +2114,9 @@
           <t>enfant-m|J'ai demandé.
 enfant-m|Papa a pris le petit pot.
 papa|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|La serviette jaune reste à sa place.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La serviette jaune reste à sa place.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2144,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2189,6 +2180,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-06.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>cuisine et jardin</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Didier, papa</t>
+          <t>Nino, papa, maman</t>
         </is>
       </c>
     </row>
